--- a/data/trans_dic/IP31KM12_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM12_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,43; 100,0</t>
+          <t>88,12; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,76; 100,0</t>
+          <t>91,15; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,39; 99,13</t>
+          <t>92,33; 99,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,24; 98,17</t>
+          <t>98,51; 99,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>98,58; 99,79</t>
+          <t>94,6; 97,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97,33; 98,82</t>
+          <t>97,19; 98,74</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,37; 99,06</t>
+          <t>96,4; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,02; 100,0</t>
+          <t>95,79; 99,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,74; 99,32</t>
+          <t>97,12; 99,36</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,98; 98,15</t>
+          <t>98,26; 99,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>98,26; 99,56</t>
+          <t>95,62; 97,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,47; 98,77</t>
+          <t>97,32; 98,65</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52494</t>
+          <t>51670</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56251</t>
+          <t>44636</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108744</t>
+          <t>96306</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>49637; 53699</t>
+          <t>47334; 53715</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51789; 58345</t>
+          <t>41841; 45905</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103519; 111067</t>
+          <t>91976; 98621</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>606</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>437736</t>
+          <t>463775</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>502313</t>
+          <t>410248</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>940049</t>
+          <t>874024</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>430322; 443543</t>
+          <t>459464; 465543</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>498094; 504167</t>
+          <t>401754; 415669</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>931497; 945802</t>
+          <t>866018; 879885</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>216</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>143039</t>
+          <t>165120</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>179439</t>
+          <t>144164</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322477</t>
+          <t>309283</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>139413; 144815</t>
+          <t>160693; 166686</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>175735; 181139</t>
+          <t>140940; 146134</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316638; 325114</t>
+          <t>304777; 311813</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>887</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>633268</t>
+          <t>680565</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>738002</t>
+          <t>599048</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1371270</t>
+          <t>1279613</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>625521; 639653</t>
+          <t>674888; 684044</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>731772; 741486</t>
+          <t>590631; 605225</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1361117; 1379267</t>
+          <t>1269533; 1286966</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM12_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM12_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan todos los días (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>96,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>88,12; 100,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>91,15; 100,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>92,33; 99,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>98,51; 99,81</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>94,6; 97,88</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>97,19; 98,74</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>96,4; 100,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>95,79; 99,32</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>97,12; 99,36</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>98,26; 99,6</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>95,62; 97,98</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>97,32; 98,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9619282323505547</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9723537144888195</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9667323063917515</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>51670</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>44636</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>96306</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.881206561848294</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9114600691411835</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9232721428199908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>47334; 53715</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>41841; 45905</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>91976; 98621</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9899724831431611</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1231</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9943231854088757</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9660489696657644</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9808485499484372</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>463775</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>410248</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>874024</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9850801264408277</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9460479643286616</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9718636298881537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>459464; 465543</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>401754; 415669</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>866018; 879885</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9981125752565817</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9788149569154617</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9874252590592222</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9906058849566892</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9797745890418784</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9855275379029638</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>165120</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>144164</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>309283</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9640480189656456</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.957861253898935</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9711696116085738</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>160693; 166686</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>140940; 146134</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>304777; 311813</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9931629946212992</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9935897973323851</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9908875051379264</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9697869669445957</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9808961772776337</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>680565</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>599048</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1279613</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9826209889953467</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9561602434901842</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.9731693336655332</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>674888; 684044</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>590631; 605225</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1269533; 1286966</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9959517066210481</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9797859026298399</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9865325077544217</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan todos los días (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>51670</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>44636</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>96306</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>47334</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>41841</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>91976</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>53715</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>45905</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>98621</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>625</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>606</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>463775</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>410248</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>874024</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>459464</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>401754</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>866018</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>465543</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>415669</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>879885</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>231</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>165120</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>144164</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>309283</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>160693</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>140940</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>304777</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>166686</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>146134</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>311813</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>931</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>887</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>680565</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>599048</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1279613</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>674888</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>590631</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1269533</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>684044</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>605225</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1286966</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>